--- a/data/credit_bond_2026-09-22.xlsx
+++ b/data/credit_bond_2026-09-22.xlsx
@@ -739,7 +739,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6025/1.6000</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -924,7 +924,11 @@
           <t>09-22 18:00</t>
         </is>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>102683784.IB</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -963,7 +967,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.1100/2.0800</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -1003,7 +1007,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X4" s="3"/>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>2.20%~2.30%</t>
+        </is>
+      </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -1131,7 +1139,9 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="AZ4" s="3"/>
+      <c r="AZ4" s="4" t="n">
+        <v>0.03</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_2026-09-22.xlsx
+++ b/data/credit_bond_2026-09-22.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-22" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-23" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>1.6025/1.6000</t>
+          <t>1.6025/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>A- 65.00</t>
+          <t>A- 60.77</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>2.1100/2.0800</t>
+          <t>2.1200/2.0700</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 39.83</t>
+          <t>B- 39.58</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1000,8 +1000,12 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
+      <c r="U4" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>5.53</v>
+      </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
           <t>6+</t>

--- a/data/credit_bond_2026-09-22.xlsx
+++ b/data/credit_bond_2026-09-22.xlsx
@@ -700,7 +700,11 @@
           <t>09-22 18:00</t>
         </is>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>222680027.IB</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -709,14 +713,20 @@
       <c r="E3" s="4" t="n">
         <v>30.0</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="4" t="n">
+        <v>30.0</v>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>1.40 ~ 1.80</t>
         </is>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>36.53</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>1.66</t>
@@ -937,14 +947,20 @@
       <c r="E4" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>1.70 ~ 2.70</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>81.53</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>2.14</t>

--- a/data/credit_bond_2026-09-22.xlsx
+++ b/data/credit_bond_2026-09-22.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-23" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-24" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26北部湾银行绿债01</t>
+          <t>26西安高新MTN010</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>222680027.IB</t>
+          <t>102683784.IB</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -711,55 +711,55 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>30.0</v>
+        <v>10.0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>30.0</v>
+        <v>10.0</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>36.53</v>
+        <v>81.53</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>25北部湾银行绿债01</t>
+          <t>26西安高新MTN009</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>1.97Y</t>
+          <t>2.94Y</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>1.6095</t>
+          <t>2.1260</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>1.6025/--</t>
+          <t>2.1200/2.0700</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>广西北部湾银行股份有限公司</t>
+          <t>西安高新控股有限公司</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>A- 60.77</t>
+          <t>B- 37.93</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -779,19 +779,23 @@
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>5.53</v>
+      </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>2.20%~2.30%</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
@@ -799,30 +803,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z3" s="3"/>
       <c r="AA3" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-南宁市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准,用于《绿色金融支持项目目录(2025年版)》规定的绿色产业项目。募集资金闲置期间,发行人可以将募集资金投资于非金融企业发行的绿色债券以及具有良好信用等级和市场流动性的货币市场工具。</t>
+          <t>发行人本次中期票据注册金额为120亿元，拟全部用于偿还发行人到期债务[25西安高新CP001，25西安高新CP003，25西安高新CP004，25西安高新CP005，25西安高新CP006，25西安高新CP007，25西安高新CP008，25西安高新CP009，25西安高新CP0，25西安高新CP011，25西安高新SCP006，25西安高新SCP007，25西安高新SCP008，16西安高新MTN002，25西安高新CP012，25西安高新CP013，25西安高新CP014，26西安高新CP001，24西安高新MTN001]</t>
         </is>
       </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中国银行股份有限公司,兴业银行股份有限公司,光大证券股份有限公司,国海证券股份有限公司</t>
+          <t>长安银行股份有限公司,广发银行股份有限公司</t>
         </is>
       </c>
       <c r="AD3" s="3"/>
       <c r="AE3" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF3" s="3" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AH3" s="3" t="inlineStr">
         <is>
-          <t>广西北部湾银行股份有限公司2026年绿色金融债券(第一期)</t>
+          <t>西安高新控股有限公司2026年度第十期中期票据</t>
         </is>
       </c>
       <c r="AI3" s="3" t="inlineStr">
@@ -847,60 +847,64 @@
       </c>
       <c r="AJ3" s="3" t="inlineStr">
         <is>
-          <t>2029-09-24</t>
-        </is>
-      </c>
-      <c r="AK3" s="3"/>
+          <t>2029-09-23</t>
+        </is>
+      </c>
+      <c r="AK3" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL3" s="3" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AO3" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ3" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AR3" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>城商行</t>
-        </is>
-      </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -921,12 +925,14 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="AZ3" s="3"/>
+      <c r="AZ3" s="4" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26西安高新MTN010</t>
+          <t>26北部湾银行绿债01</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -936,7 +942,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>102683784.IB</t>
+          <t>222680027.IB</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -945,55 +951,55 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>10.0</v>
+        <v>30.0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>10.0</v>
+        <v>30.0</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>81.53</v>
+        <v>36.53</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>26西安高新MTN009</t>
+          <t>25北部湾银行绿债01</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>1.97Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>2.1260</t>
+          <t>1.6095</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>2.1200/2.0700</t>
+          <t>1.6025/--</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>西安高新控股有限公司</t>
+          <t>广西北部湾银行股份有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 39.58</t>
+          <t>B+ 56.97</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1013,23 +1019,19 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>5.53</v>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>2.20%~2.30%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -1037,26 +1039,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z4" s="3"/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>广西壮族自治区-南宁市</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>发行人本次中期票据注册金额为120亿元，拟全部用于偿还发行人到期债务[25西安高新CP001，25西安高新CP003，25西安高新CP004，25西安高新CP005，25西安高新CP006，25西安高新CP007，25西安高新CP008，25西安高新CP009，25西安高新CP0，25西安高新CP011，25西安高新SCP006，25西安高新SCP007，25西安高新SCP008，16西安高新MTN002，25西安高新CP012，25西安高新CP013，25西安高新CP014，26西安高新CP001，24西安高新MTN001]</t>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准,用于《绿色金融支持项目目录(2025年版)》规定的绿色产业项目。募集资金闲置期间,发行人可以将募集资金投资于非金融企业发行的绿色债券以及具有良好信用等级和市场流动性的货币市场工具。</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>长安银行股份有限公司,广发银行股份有限公司</t>
+          <t>中信证券股份有限公司,中国银行股份有限公司,兴业银行股份有限公司,光大证券股份有限公司,国海证券股份有限公司</t>
         </is>
       </c>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
@@ -1071,7 +1077,7 @@
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>西安高新控股有限公司2026年度第十期中期票据</t>
+          <t>广西北部湾银行股份有限公司2026年绿色金融债券(第一期)</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
@@ -1081,57 +1087,53 @@
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2029-09-23</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-24</t>
+        </is>
+      </c>
+      <c r="AK4" s="3"/>
       <c r="AL4" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AM4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU4" s="3" t="inlineStr">
@@ -1159,9 +1161,7 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="AZ4" s="4" t="n">
-        <v>0.03</v>
-      </c>
+      <c r="AZ4" s="3"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_2026-09-22.xlsx
+++ b/data/credit_bond_2026-09-22.xlsx
@@ -692,7 +692,7 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26西安高新MTN010</t>
+          <t>26北部湾银行绿债01</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>102683784.IB</t>
+          <t>222680027.IB</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -711,55 +711,55 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>10.0</v>
+        <v>30.0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>10.0</v>
+        <v>30.0</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>81.53</v>
+        <v>36.53</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>26西安高新MTN009</t>
+          <t>25北部湾银行绿债01</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>1.97Y</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>2.1260</t>
+          <t>1.6095</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>2.1200/2.0700</t>
+          <t>1.6025/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>西安高新控股有限公司</t>
+          <t>广西北部湾银行股份有限公司</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>B- 37.93</t>
+          <t>B+ 56.97</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -774,28 +774,24 @@
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="U3" s="4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V3" s="4" t="n">
-        <v>5.53</v>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>2.20%~2.30%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
@@ -803,26 +799,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z3" s="3"/>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA3" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>广西壮族自治区-南宁市</t>
         </is>
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>发行人本次中期票据注册金额为120亿元，拟全部用于偿还发行人到期债务[25西安高新CP001，25西安高新CP003，25西安高新CP004，25西安高新CP005，25西安高新CP006，25西安高新CP007，25西安高新CP008，25西安高新CP009，25西安高新CP0，25西安高新CP011，25西安高新SCP006，25西安高新SCP007，25西安高新SCP008，16西安高新MTN002，25西安高新CP012，25西安高新CP013，25西安高新CP014，26西安高新CP001，24西安高新MTN001]</t>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准,用于《绿色金融支持项目目录(2025年版)》规定的绿色产业项目。募集资金闲置期间,发行人可以将募集资金投资于非金融企业发行的绿色债券以及具有良好信用等级和市场流动性的货币市场工具。</t>
         </is>
       </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
-          <t>长安银行股份有限公司,广发银行股份有限公司</t>
+          <t>中信证券股份有限公司,中国银行股份有限公司,兴业银行股份有限公司,光大证券股份有限公司,国海证券股份有限公司</t>
         </is>
       </c>
       <c r="AD3" s="3"/>
       <c r="AE3" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF3" s="3" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AH3" s="3" t="inlineStr">
         <is>
-          <t>西安高新控股有限公司2026年度第十期中期票据</t>
+          <t>广西北部湾银行股份有限公司2026年绿色金融债券(第一期)</t>
         </is>
       </c>
       <c r="AI3" s="3" t="inlineStr">
@@ -847,57 +847,53 @@
       </c>
       <c r="AJ3" s="3" t="inlineStr">
         <is>
-          <t>2029-09-23</t>
-        </is>
-      </c>
-      <c r="AK3" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-24</t>
+        </is>
+      </c>
+      <c r="AK3" s="3"/>
       <c r="AL3" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AM3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP3" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ3" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT3" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU3" s="3" t="inlineStr">
@@ -925,14 +921,12 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="AZ3" s="4" t="n">
-        <v>0.03</v>
-      </c>
+      <c r="AZ3" s="3"/>
     </row>
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26北部湾银行绿债01</t>
+          <t>26西安高新MTN010</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -942,7 +936,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>222680027.IB</t>
+          <t>102683784.IB</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -951,55 +945,55 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>30.0</v>
+        <v>10.0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>30.0</v>
+        <v>10.0</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>36.53</v>
+        <v>81.53</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>25北部湾银行绿债01</t>
+          <t>26西安高新MTN009</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>1.97Y</t>
+          <t>2.94Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1.6095</t>
+          <t>2.1260</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>1.6025/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>广西北部湾银行股份有限公司</t>
+          <t>西安高新控股有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B+ 56.97</t>
+          <t>B- 37.93</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1014,24 +1008,28 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>5.53</v>
+      </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>2.20%~2.30%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -1039,30 +1037,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-南宁市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准,用于《绿色金融支持项目目录(2025年版)》规定的绿色产业项目。募集资金闲置期间,发行人可以将募集资金投资于非金融企业发行的绿色债券以及具有良好信用等级和市场流动性的货币市场工具。</t>
+          <t>发行人本次中期票据注册金额为120亿元，拟全部用于偿还发行人到期债务[25西安高新CP001，25西安高新CP003，25西安高新CP004，25西安高新CP005，25西安高新CP006，25西安高新CP007，25西安高新CP008，25西安高新CP009，25西安高新CP0，25西安高新CP011，25西安高新SCP006，25西安高新SCP007，25西安高新SCP008，16西安高新MTN002，25西安高新CP012，25西安高新CP013，25西安高新CP014，26西安高新CP001，24西安高新MTN001]</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中国银行股份有限公司,兴业银行股份有限公司,光大证券股份有限公司,国海证券股份有限公司</t>
+          <t>长安银行股份有限公司,广发银行股份有限公司</t>
         </is>
       </c>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
@@ -1077,7 +1071,7 @@
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>广西北部湾银行股份有限公司2026年绿色金融债券(第一期)</t>
+          <t>西安高新控股有限公司2026年度第十期中期票据</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
@@ -1087,60 +1081,64 @@
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2029-09-24</t>
-        </is>
-      </c>
-      <c r="AK4" s="3"/>
+          <t>2029-09-23</t>
+        </is>
+      </c>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL4" s="3" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AO4" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ4" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AR4" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>城商行</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV4" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -1161,7 +1159,9 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="AZ4" s="3"/>
+      <c r="AZ4" s="4" t="n">
+        <v>0.03</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_2026-09-22.xlsx
+++ b/data/credit_bond_2026-09-22.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-24" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-25" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -37,10 +37,6 @@
       <sz val="12.0"/>
       <color indexed="8"/>
       <b val="true"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <sz val="12.0"/>
     </font>
   </fonts>
   <fills count="5">
@@ -94,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
       <alignment horizontal="center" wrapText="true" vertical="center"/>
@@ -103,12 +99,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
       <alignment horizontal="center" wrapText="true" vertical="center"/>
       <protection locked="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyBorder="true" applyFont="true">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyBorder="true" applyFont="true">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
 </styleSheet>
@@ -159,7 +149,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ1"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -173,257 +163,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
     </row>
@@ -687,480 +677,6 @@
         <is>
           <t>团费(%)</t>
         </is>
-      </c>
-    </row>
-    <row r="3" customHeight="true" ht="18.0">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>26北部湾银行绿债01</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>09-22 18:00</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>222680027.IB</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>3Y</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>1.40 ~ 1.80</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>36.53</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>25北部湾银行绿债01</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>1.97Y</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>1.6095</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>1.6025/--</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>广西北部湾银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>B+ 56.97</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>09-22 09:00</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3" t="inlineStr">
-        <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>1.63%~1.73%</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="AA3" s="3" t="inlineStr">
-        <is>
-          <t>广西壮族自治区-南宁市</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="inlineStr">
-        <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准,用于《绿色金融支持项目目录(2025年版)》规定的绿色产业项目。募集资金闲置期间,发行人可以将募集资金投资于非金融企业发行的绿色债券以及具有良好信用等级和市场流动性的货币市场工具。</t>
-        </is>
-      </c>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>中信证券股份有限公司,中国银行股份有限公司,兴业银行股份有限公司,光大证券股份有限公司,国海证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3" t="inlineStr">
-        <is>
-          <t>商业银行普通债券</t>
-        </is>
-      </c>
-      <c r="AF3" s="3" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="AG3" s="3" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="AH3" s="3" t="inlineStr">
-        <is>
-          <t>广西北部湾银行股份有限公司2026年绿色金融债券(第一期)</t>
-        </is>
-      </c>
-      <c r="AI3" s="3" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="AJ3" s="3" t="inlineStr">
-        <is>
-          <t>2029-09-24</t>
-        </is>
-      </c>
-      <c r="AK3" s="3"/>
-      <c r="AL3" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AO3" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ3" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AR3" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>城商行</t>
-        </is>
-      </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV3" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW3" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX3" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AZ3" s="3"/>
-    </row>
-    <row r="4" customHeight="true" ht="18.0">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>26西安高新MTN010</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>09-22 18:00</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>102683784.IB</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>3Y</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>81.53</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>26西安高新MTN009</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>2.94Y</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>2.1260</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>西安高新控股有限公司</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>B- 37.93</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>09-22 09:00</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>2.7</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>2.20%~2.30%</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>陕西省-西安市</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>发行人本次中期票据注册金额为120亿元，拟全部用于偿还发行人到期债务[25西安高新CP001，25西安高新CP003，25西安高新CP004，25西安高新CP005，25西安高新CP006，25西安高新CP007，25西安高新CP008，25西安高新CP009，25西安高新CP0，25西安高新CP011，25西安高新SCP006，25西安高新SCP007，25西安高新SCP008，16西安高新MTN002，25西安高新CP012，25西安高新CP013，25西安高新CP014，26西安高新CP001，24西安高新MTN001]</t>
-        </is>
-      </c>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>长安银行股份有限公司,广发银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD4" s="3"/>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="AF4" s="3" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="AG4" s="3" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="AH4" s="3" t="inlineStr">
-        <is>
-          <t>西安高新控股有限公司2026年度第十期中期票据</t>
-        </is>
-      </c>
-      <c r="AI4" s="3" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="AJ4" s="3" t="inlineStr">
-        <is>
-          <t>2029-09-23</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AM4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AO4" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AQ4" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR4" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV4" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW4" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX4" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AZ4" s="4" t="n">
-        <v>0.03</v>
       </c>
     </row>
   </sheetData>

--- a/data/credit_bond_2026-09-22.xlsx
+++ b/data/credit_bond_2026-09-22.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-25" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-28" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -163,257 +163,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
     </row>
